--- a/n1_lyrica_v3.xlsx
+++ b/n1_lyrica_v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/70ed252595cc6131/Anexos/stats/teixeira/lyrica/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="8_{B27AD87D-98AD-422C-B062-FEDF74E54619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{263C77F3-A288-4C9D-8560-0253B7C25A65}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{B27AD87D-98AD-422C-B062-FEDF74E54619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8119DB5-5C34-4C80-A1F5-76FA1EC6254B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11040" xr2:uid="{94362CDF-6C5D-4417-A2BE-F689EA0486F5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="33">
   <si>
     <t>date</t>
   </si>
@@ -132,7 +132,10 @@
     <t>day2</t>
   </si>
   <si>
-    <t>obs_order</t>
+    <t>obs_order_cycle</t>
+  </si>
+  <si>
+    <t>obs_order_period</t>
   </si>
 </sst>
 </file>
@@ -205,19 +208,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FAD2191-F206-4B96-8366-D47C764298D0}" name="Tabela1" displayName="Tabela1" ref="A1:W46" totalsRowShown="0">
-  <autoFilter ref="A1:W46" xr:uid="{0FAD2191-F206-4B96-8366-D47C764298D0}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FAD2191-F206-4B96-8366-D47C764298D0}" name="Tabela1" displayName="Tabela1" ref="A1:X46" totalsRowShown="0">
+  <autoFilter ref="A1:X46" xr:uid="{0FAD2191-F206-4B96-8366-D47C764298D0}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W41">
     <sortCondition ref="C1:C41"/>
   </sortState>
-  <tableColumns count="23">
+  <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{EEFBEE00-D493-40DC-92D6-AFFA40239080}" name="date" dataDxfId="1"/>
     <tableColumn id="16" xr3:uid="{30BAF7A3-909A-4E28-8020-B684EAE0D7D1}" name="d" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{77CAD242-3C2D-4EED-8D68-00E184EC9C43}" name="day"/>
     <tableColumn id="3" xr3:uid="{4E3C930C-8192-4A04-BA00-DCBC655547D0}" name="cycle"/>
     <tableColumn id="4" xr3:uid="{C56B3168-3BA9-4F60-91F2-D557C3684C2C}" name="treat"/>
     <tableColumn id="5" xr3:uid="{6734E705-8671-42EF-855D-BC4733B04E2F}" name="order"/>
-    <tableColumn id="17" xr3:uid="{95763741-DE4C-453F-A01E-5E957C1DBC30}" name="obs_order"/>
+    <tableColumn id="17" xr3:uid="{95763741-DE4C-453F-A01E-5E957C1DBC30}" name="obs_order_period"/>
+    <tableColumn id="18" xr3:uid="{C2AE19BE-585D-4C53-B7D0-4DF7E3AA34D5}" name="obs_order_cycle"/>
     <tableColumn id="19" xr3:uid="{7B4C7719-06F8-4615-91D6-BF72E2583EF8}" name="eye_pain_morn"/>
     <tableColumn id="6" xr3:uid="{7EE843D3-7FF3-4793-8A08-78286A8352EA}" name="sleep_ordinal"/>
     <tableColumn id="7" xr3:uid="{D2CD69ED-9DE9-457B-92AC-8E035CF687C7}" name="sleep_cont"/>
@@ -536,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D88D48-57DE-49F5-B1C2-4D6C6D40FFB9}">
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:X46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
@@ -544,14 +548,14 @@
     <col min="3" max="3" width="7.42578125" customWidth="1"/>
     <col min="4" max="4" width="6.140625" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="7" width="7.42578125" customWidth="1"/>
-    <col min="8" max="15" width="8.7109375" customWidth="1"/>
-    <col min="16" max="16" width="6.140625" customWidth="1"/>
-    <col min="17" max="20" width="8.42578125" customWidth="1"/>
-    <col min="21" max="23" width="8.7109375" customWidth="1"/>
+    <col min="6" max="8" width="7.42578125" customWidth="1"/>
+    <col min="9" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="17" width="6.140625" customWidth="1"/>
+    <col min="18" max="21" width="8.42578125" customWidth="1"/>
+    <col min="22" max="24" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -571,58 +575,61 @@
         <v>3</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45966</v>
       </c>
@@ -645,37 +652,40 @@
         <v>1</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>28</v>
       </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
       <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
         <v>25</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>30</v>
       </c>
-      <c r="N2">
-        <v>2</v>
-      </c>
       <c r="O2">
+        <v>2</v>
+      </c>
+      <c r="P2">
         <v>29</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>25</v>
       </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-      <c r="U2" t="s">
-        <v>20</v>
-      </c>
-      <c r="W2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="V2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45967</v>
       </c>
@@ -698,43 +708,46 @@
         <v>2</v>
       </c>
       <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>22</v>
       </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
       <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
         <v>32</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>28</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>10</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>18</v>
       </c>
-      <c r="N3">
-        <v>2</v>
-      </c>
       <c r="O3">
+        <v>2</v>
+      </c>
+      <c r="P3">
         <v>22</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>31</v>
       </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="U3" t="s">
-        <v>20</v>
-      </c>
-      <c r="W3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="V3" t="s">
+        <v>20</v>
+      </c>
+      <c r="X3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45968</v>
       </c>
@@ -757,40 +770,43 @@
         <v>3</v>
       </c>
       <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>28</v>
       </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
       <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
         <v>18</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>22</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>10</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>16</v>
       </c>
-      <c r="N4">
-        <v>2</v>
-      </c>
       <c r="O4">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="P4">
+        <v>20</v>
+      </c>
+      <c r="Q4">
         <v>32</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>0</v>
       </c>
-      <c r="W4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45969</v>
       </c>
@@ -813,43 +829,46 @@
         <v>4</v>
       </c>
       <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
         <v>23</v>
       </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
       <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
         <v>38</v>
       </c>
-      <c r="K5">
-        <v>20</v>
-      </c>
       <c r="L5">
+        <v>20</v>
+      </c>
+      <c r="M5">
         <v>10</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>14</v>
       </c>
-      <c r="N5">
-        <v>2</v>
-      </c>
       <c r="O5">
+        <v>2</v>
+      </c>
+      <c r="P5">
         <v>24</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>27</v>
       </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="U5" t="s">
-        <v>20</v>
-      </c>
-      <c r="W5">
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="V5" t="s">
+        <v>20</v>
+      </c>
+      <c r="X5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45970</v>
       </c>
@@ -872,37 +891,40 @@
         <v>5</v>
       </c>
       <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
         <v>18</v>
       </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
       <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
         <v>24</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>25</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>9.75</v>
       </c>
-      <c r="N6">
-        <v>2</v>
-      </c>
       <c r="O6">
+        <v>2</v>
+      </c>
+      <c r="P6">
         <v>23</v>
       </c>
-      <c r="P6">
-        <v>20</v>
-      </c>
       <c r="Q6">
+        <v>20</v>
+      </c>
+      <c r="R6">
         <v>0</v>
       </c>
-      <c r="W6">
+      <c r="X6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45980</v>
       </c>
@@ -925,43 +947,46 @@
         <v>1</v>
       </c>
       <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
         <v>21</v>
       </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
       <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
         <v>18</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>35</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>8.5</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>14</v>
       </c>
-      <c r="N7">
-        <v>2</v>
-      </c>
       <c r="O7">
+        <v>2</v>
+      </c>
+      <c r="P7">
         <v>24</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>28</v>
       </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="V7" t="s">
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="W7" t="s">
         <v>22</v>
       </c>
-      <c r="W7">
+      <c r="X7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45981</v>
       </c>
@@ -984,40 +1009,43 @@
         <v>2</v>
       </c>
       <c r="H8">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8">
         <v>23</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>28</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>9.5</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>15</v>
       </c>
-      <c r="N8">
-        <v>2</v>
-      </c>
       <c r="O8">
+        <v>2</v>
+      </c>
+      <c r="P8">
         <v>27</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>23</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>0</v>
       </c>
-      <c r="W8">
+      <c r="X8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45982</v>
       </c>
@@ -1040,40 +1068,43 @@
         <v>3</v>
       </c>
       <c r="H9">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9">
         <v>29</v>
       </c>
-      <c r="K9">
-        <v>20</v>
-      </c>
       <c r="L9">
+        <v>20</v>
+      </c>
+      <c r="M9">
         <v>9.6999999999999993</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>15</v>
       </c>
-      <c r="N9">
-        <v>2</v>
-      </c>
       <c r="O9">
+        <v>2</v>
+      </c>
+      <c r="P9">
         <v>23</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>24</v>
       </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="W9">
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="X9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45983</v>
       </c>
@@ -1096,37 +1127,40 @@
         <v>4</v>
       </c>
       <c r="H10">
+        <v>9</v>
+      </c>
+      <c r="I10">
         <v>25</v>
       </c>
-      <c r="I10">
-        <v>3</v>
-      </c>
       <c r="J10">
+        <v>3</v>
+      </c>
+      <c r="K10">
         <v>35</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>24</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>11.5</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>16</v>
       </c>
-      <c r="N10">
-        <v>2</v>
-      </c>
       <c r="O10">
+        <v>2</v>
+      </c>
+      <c r="P10">
         <v>25</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>30</v>
       </c>
-      <c r="W10">
+      <c r="X10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45984</v>
       </c>
@@ -1149,40 +1183,43 @@
         <v>5</v>
       </c>
       <c r="H11">
+        <v>10</v>
+      </c>
+      <c r="I11">
         <v>25</v>
       </c>
-      <c r="I11">
-        <v>3</v>
-      </c>
       <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11">
         <v>36</v>
       </c>
-      <c r="K11">
-        <v>20</v>
-      </c>
       <c r="L11">
+        <v>20</v>
+      </c>
+      <c r="M11">
         <v>12</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>14</v>
       </c>
-      <c r="N11">
-        <v>2</v>
-      </c>
       <c r="O11">
+        <v>2</v>
+      </c>
+      <c r="P11">
         <v>22</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>26</v>
       </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
-      <c r="W11">
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="X11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45994</v>
       </c>
@@ -1205,40 +1242,43 @@
         <v>1</v>
       </c>
       <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
         <v>22</v>
       </c>
-      <c r="I12">
-        <v>2</v>
-      </c>
       <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12">
         <v>24</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>33</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>10.5</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>14</v>
       </c>
-      <c r="N12">
-        <v>2</v>
-      </c>
       <c r="O12">
+        <v>2</v>
+      </c>
+      <c r="P12">
         <v>22</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>27</v>
       </c>
-      <c r="Q12">
-        <v>1</v>
-      </c>
-      <c r="W12">
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="X12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45995</v>
       </c>
@@ -1261,40 +1301,43 @@
         <v>2</v>
       </c>
       <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
         <v>25</v>
       </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
       <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
         <v>22</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>35</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>10.6</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>14</v>
       </c>
-      <c r="N13">
-        <v>2</v>
-      </c>
       <c r="O13">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="P13">
+        <v>20</v>
+      </c>
+      <c r="Q13">
         <v>26</v>
       </c>
-      <c r="Q13">
-        <v>1</v>
-      </c>
-      <c r="W13">
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="X13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45996</v>
       </c>
@@ -1317,43 +1360,46 @@
         <v>3</v>
       </c>
       <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
         <v>25</v>
       </c>
-      <c r="I14">
-        <v>2</v>
-      </c>
       <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14">
         <v>16</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>30</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>10.8</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>14</v>
       </c>
-      <c r="N14">
-        <v>2</v>
-      </c>
       <c r="O14">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="P14">
+        <v>20</v>
+      </c>
+      <c r="Q14">
         <v>25</v>
       </c>
-      <c r="Q14">
-        <v>1</v>
-      </c>
-      <c r="V14" t="s">
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="W14" t="s">
         <v>23</v>
       </c>
-      <c r="W14">
+      <c r="X14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45997</v>
       </c>
@@ -1376,40 +1422,43 @@
         <v>4</v>
       </c>
       <c r="H15">
+        <v>4</v>
+      </c>
+      <c r="I15">
         <v>24</v>
       </c>
-      <c r="I15">
-        <v>3</v>
-      </c>
       <c r="J15">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="K15">
         <v>33</v>
       </c>
       <c r="L15">
+        <v>33</v>
+      </c>
+      <c r="M15">
         <v>10.9</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>14</v>
       </c>
-      <c r="N15">
-        <v>2</v>
-      </c>
       <c r="O15">
+        <v>2</v>
+      </c>
+      <c r="P15">
         <v>22</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>26</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>0</v>
       </c>
-      <c r="W15">
+      <c r="X15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45998</v>
       </c>
@@ -1432,40 +1481,43 @@
         <v>5</v>
       </c>
       <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16">
         <v>24</v>
       </c>
-      <c r="I16">
-        <v>2</v>
-      </c>
       <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16">
         <v>25</v>
       </c>
-      <c r="K16">
-        <v>20</v>
-      </c>
       <c r="L16">
+        <v>20</v>
+      </c>
+      <c r="M16">
         <v>10.8</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>14</v>
       </c>
-      <c r="N16">
-        <v>3</v>
-      </c>
       <c r="O16">
+        <v>3</v>
+      </c>
+      <c r="P16">
         <v>35</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>30</v>
       </c>
-      <c r="Q16">
-        <v>1</v>
-      </c>
-      <c r="W16">
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="X16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46008</v>
       </c>
@@ -1488,37 +1540,40 @@
         <v>1</v>
       </c>
       <c r="H17">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
         <v>18</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>25</v>
       </c>
-      <c r="N17">
-        <v>2</v>
-      </c>
       <c r="O17">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="P17">
         <v>25</v>
       </c>
       <c r="Q17">
-        <v>1</v>
-      </c>
-      <c r="R17" t="s">
-        <v>20</v>
-      </c>
-      <c r="W17">
+        <v>25</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17" t="s">
+        <v>20</v>
+      </c>
+      <c r="X17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46009</v>
       </c>
@@ -1541,43 +1596,46 @@
         <v>2</v>
       </c>
       <c r="H18">
+        <v>7</v>
+      </c>
+      <c r="I18">
         <v>18</v>
       </c>
-      <c r="I18">
-        <v>3</v>
-      </c>
       <c r="J18">
+        <v>3</v>
+      </c>
+      <c r="K18">
         <v>36</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>28</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>9</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>14</v>
       </c>
-      <c r="N18">
-        <v>3</v>
-      </c>
       <c r="O18">
+        <v>3</v>
+      </c>
+      <c r="P18">
         <v>33</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>29</v>
       </c>
-      <c r="Q18">
-        <v>1</v>
-      </c>
-      <c r="R18" t="s">
-        <v>20</v>
-      </c>
-      <c r="W18">
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18" t="s">
+        <v>20</v>
+      </c>
+      <c r="X18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46010</v>
       </c>
@@ -1600,43 +1658,46 @@
         <v>3</v>
       </c>
       <c r="H19">
+        <v>8</v>
+      </c>
+      <c r="I19">
         <v>24</v>
       </c>
-      <c r="I19">
-        <v>3</v>
-      </c>
       <c r="J19">
+        <v>3</v>
+      </c>
+      <c r="K19">
         <v>30</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>38</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>4</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>38</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>35</v>
       </c>
-      <c r="Q19">
-        <v>1</v>
-      </c>
-      <c r="R19" t="s">
-        <v>20</v>
-      </c>
-      <c r="U19" t="s">
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19" t="s">
         <v>20</v>
       </c>
       <c r="V19" t="s">
+        <v>20</v>
+      </c>
+      <c r="W19" t="s">
         <v>24</v>
       </c>
-      <c r="W19">
+      <c r="X19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46011</v>
       </c>
@@ -1659,43 +1720,46 @@
         <v>4</v>
       </c>
       <c r="H20">
+        <v>9</v>
+      </c>
+      <c r="I20">
         <v>25</v>
       </c>
-      <c r="I20">
-        <v>3</v>
-      </c>
       <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20">
         <v>26</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>22</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>9.75</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>14</v>
       </c>
-      <c r="N20">
-        <v>3</v>
-      </c>
       <c r="O20">
+        <v>3</v>
+      </c>
+      <c r="P20">
         <v>32</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>35</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>0</v>
       </c>
-      <c r="R20" t="s">
-        <v>20</v>
-      </c>
-      <c r="W20">
+      <c r="S20" t="s">
+        <v>20</v>
+      </c>
+      <c r="X20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46012</v>
       </c>
@@ -1718,43 +1782,46 @@
         <v>5</v>
       </c>
       <c r="H21">
+        <v>10</v>
+      </c>
+      <c r="I21">
         <v>19</v>
       </c>
-      <c r="I21">
-        <v>2</v>
-      </c>
       <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21">
         <v>22</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>27</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>10</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>15</v>
       </c>
-      <c r="N21">
-        <v>3</v>
-      </c>
       <c r="O21">
+        <v>3</v>
+      </c>
+      <c r="P21">
         <v>34</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>32</v>
       </c>
-      <c r="Q21">
-        <v>1</v>
-      </c>
-      <c r="R21" t="s">
-        <v>20</v>
-      </c>
-      <c r="W21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21" t="s">
+        <v>20</v>
+      </c>
+      <c r="X21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46022</v>
       </c>
@@ -1777,37 +1844,40 @@
         <v>1</v>
       </c>
       <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
         <v>22</v>
       </c>
-      <c r="I22">
-        <v>2</v>
-      </c>
       <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
         <v>22</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>30</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>10</v>
       </c>
-      <c r="N22">
-        <v>3</v>
-      </c>
       <c r="O22">
+        <v>3</v>
+      </c>
+      <c r="P22">
         <v>33</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>22</v>
       </c>
-      <c r="Q22">
-        <v>1</v>
-      </c>
-      <c r="W22">
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="X22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46023</v>
       </c>
@@ -1830,37 +1900,40 @@
         <v>2</v>
       </c>
       <c r="H23">
+        <v>2</v>
+      </c>
+      <c r="I23">
         <v>27</v>
       </c>
-      <c r="I23">
-        <v>3</v>
-      </c>
       <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23">
         <v>29</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>26</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>10.5</v>
       </c>
-      <c r="N23">
-        <v>2</v>
-      </c>
       <c r="O23">
+        <v>2</v>
+      </c>
+      <c r="P23">
         <v>24</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>25</v>
       </c>
-      <c r="Q23">
-        <v>1</v>
-      </c>
-      <c r="W23">
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="X23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46024</v>
       </c>
@@ -1883,43 +1956,46 @@
         <v>3</v>
       </c>
       <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24">
         <v>28</v>
       </c>
-      <c r="I24">
-        <v>3</v>
-      </c>
       <c r="J24">
+        <v>3</v>
+      </c>
+      <c r="K24">
         <v>27</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>26</v>
       </c>
-      <c r="N24">
-        <v>2</v>
-      </c>
       <c r="O24">
+        <v>2</v>
+      </c>
+      <c r="P24">
         <v>26</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>30</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>0</v>
       </c>
-      <c r="R24" t="s">
-        <v>20</v>
-      </c>
       <c r="S24" t="s">
         <v>20</v>
       </c>
       <c r="T24" t="s">
         <v>20</v>
       </c>
-      <c r="W24">
+      <c r="U24" t="s">
+        <v>20</v>
+      </c>
+      <c r="X24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46025</v>
       </c>
@@ -1942,37 +2018,37 @@
         <v>4</v>
       </c>
       <c r="H25">
+        <v>4</v>
+      </c>
+      <c r="I25">
         <v>25</v>
       </c>
-      <c r="I25">
-        <v>3</v>
-      </c>
       <c r="J25">
+        <v>3</v>
+      </c>
+      <c r="K25">
         <v>29</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>28</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>10</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>21</v>
       </c>
-      <c r="N25">
-        <v>3</v>
-      </c>
       <c r="O25">
+        <v>3</v>
+      </c>
+      <c r="P25">
         <v>30</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>32</v>
       </c>
-      <c r="Q25">
-        <v>1</v>
-      </c>
-      <c r="R25" t="s">
-        <v>20</v>
+      <c r="R25">
+        <v>1</v>
       </c>
       <c r="S25" t="s">
         <v>20</v>
@@ -1980,11 +2056,14 @@
       <c r="T25" t="s">
         <v>20</v>
       </c>
-      <c r="W25">
+      <c r="U25" t="s">
+        <v>20</v>
+      </c>
+      <c r="X25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46026</v>
       </c>
@@ -2007,34 +2086,34 @@
         <v>5</v>
       </c>
       <c r="H26">
+        <v>5</v>
+      </c>
+      <c r="I26">
         <v>24</v>
       </c>
-      <c r="I26">
-        <v>3</v>
-      </c>
       <c r="J26">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="K26">
         <v>30</v>
       </c>
-      <c r="M26">
+      <c r="L26">
+        <v>30</v>
+      </c>
+      <c r="N26">
         <v>21</v>
       </c>
-      <c r="N26">
-        <v>3</v>
-      </c>
       <c r="O26">
+        <v>3</v>
+      </c>
+      <c r="P26">
         <v>33</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>29</v>
       </c>
-      <c r="Q26">
-        <v>1</v>
-      </c>
-      <c r="R26" t="s">
-        <v>20</v>
+      <c r="R26">
+        <v>1</v>
       </c>
       <c r="S26" t="s">
         <v>20</v>
@@ -2042,11 +2121,14 @@
       <c r="T26" t="s">
         <v>20</v>
       </c>
-      <c r="W26">
+      <c r="U26" t="s">
+        <v>20</v>
+      </c>
+      <c r="X26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46036</v>
       </c>
@@ -2069,43 +2151,46 @@
         <v>1</v>
       </c>
       <c r="H27">
+        <v>6</v>
+      </c>
+      <c r="I27">
         <v>25</v>
       </c>
-      <c r="I27">
-        <v>3</v>
-      </c>
       <c r="J27">
+        <v>3</v>
+      </c>
+      <c r="K27">
         <v>26</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>28</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>10.5</v>
       </c>
-      <c r="M27">
-        <v>20</v>
-      </c>
       <c r="N27">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="O27">
+        <v>2</v>
+      </c>
+      <c r="P27">
         <v>25</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>28</v>
       </c>
-      <c r="Q27">
-        <v>1</v>
-      </c>
-      <c r="S27" t="s">
-        <v>20</v>
-      </c>
-      <c r="W27">
+      <c r="R27">
+        <v>1</v>
+      </c>
+      <c r="T27" t="s">
+        <v>20</v>
+      </c>
+      <c r="X27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46037</v>
       </c>
@@ -2128,43 +2213,46 @@
         <v>2</v>
       </c>
       <c r="H28">
+        <v>7</v>
+      </c>
+      <c r="I28">
         <v>21</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>4</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>38</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>27</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>10</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>21</v>
       </c>
-      <c r="N28">
-        <v>3</v>
-      </c>
       <c r="O28">
+        <v>3</v>
+      </c>
+      <c r="P28">
         <v>26</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>28</v>
       </c>
-      <c r="Q28">
-        <v>1</v>
-      </c>
-      <c r="S28" t="s">
-        <v>20</v>
-      </c>
-      <c r="W28">
+      <c r="R28">
+        <v>1</v>
+      </c>
+      <c r="T28" t="s">
+        <v>20</v>
+      </c>
+      <c r="X28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46038</v>
       </c>
@@ -2187,40 +2275,43 @@
         <v>3</v>
       </c>
       <c r="H29">
+        <v>8</v>
+      </c>
+      <c r="I29">
         <v>23</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>4</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>36</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>26</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>21</v>
       </c>
-      <c r="N29">
-        <v>2</v>
-      </c>
       <c r="O29">
+        <v>2</v>
+      </c>
+      <c r="P29">
         <v>23</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>26</v>
       </c>
-      <c r="Q29">
-        <v>1</v>
-      </c>
-      <c r="S29" t="s">
-        <v>20</v>
-      </c>
-      <c r="W29">
+      <c r="R29">
+        <v>1</v>
+      </c>
+      <c r="T29" t="s">
+        <v>20</v>
+      </c>
+      <c r="X29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46039</v>
       </c>
@@ -2243,37 +2334,40 @@
         <v>4</v>
       </c>
       <c r="H30">
+        <v>9</v>
+      </c>
+      <c r="I30">
         <v>23</v>
       </c>
-      <c r="I30">
-        <v>3</v>
-      </c>
       <c r="J30">
+        <v>3</v>
+      </c>
+      <c r="K30">
         <v>33</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>22</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>9.5</v>
       </c>
-      <c r="N30">
-        <v>3</v>
-      </c>
       <c r="O30">
+        <v>3</v>
+      </c>
+      <c r="P30">
         <v>26</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>28</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>0</v>
       </c>
-      <c r="W30">
+      <c r="X30">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46040</v>
       </c>
@@ -2296,37 +2390,40 @@
         <v>5</v>
       </c>
       <c r="H31">
+        <v>10</v>
+      </c>
+      <c r="I31">
         <v>22</v>
       </c>
-      <c r="I31">
-        <v>3</v>
-      </c>
       <c r="J31">
+        <v>3</v>
+      </c>
+      <c r="K31">
         <v>29</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>30</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>10.5</v>
       </c>
-      <c r="N31">
-        <v>3</v>
-      </c>
       <c r="O31">
+        <v>3</v>
+      </c>
+      <c r="P31">
         <v>30</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>29</v>
       </c>
-      <c r="Q31">
-        <v>1</v>
-      </c>
-      <c r="W31">
+      <c r="R31">
+        <v>1</v>
+      </c>
+      <c r="X31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46050</v>
       </c>
@@ -2349,40 +2446,43 @@
         <v>1</v>
       </c>
       <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
         <v>31</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>5</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>50</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>30</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>19</v>
       </c>
-      <c r="N32">
-        <v>2</v>
-      </c>
       <c r="O32">
+        <v>2</v>
+      </c>
+      <c r="P32">
         <v>24</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>28</v>
       </c>
-      <c r="Q32">
-        <v>1</v>
-      </c>
-      <c r="R32" t="s">
-        <v>20</v>
-      </c>
-      <c r="W32">
+      <c r="R32">
+        <v>1</v>
+      </c>
+      <c r="S32" t="s">
+        <v>20</v>
+      </c>
+      <c r="X32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46051</v>
       </c>
@@ -2405,40 +2505,43 @@
         <v>2</v>
       </c>
       <c r="H33">
+        <v>2</v>
+      </c>
+      <c r="I33">
         <v>27</v>
       </c>
-      <c r="I33">
-        <v>3</v>
-      </c>
       <c r="J33">
+        <v>3</v>
+      </c>
+      <c r="K33">
         <v>34</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>27</v>
       </c>
-      <c r="M33">
-        <v>20</v>
-      </c>
       <c r="N33">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="O33">
+        <v>3</v>
+      </c>
+      <c r="P33">
         <v>28</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>30</v>
       </c>
-      <c r="Q33">
-        <v>1</v>
-      </c>
-      <c r="R33" t="s">
-        <v>20</v>
-      </c>
-      <c r="W33">
+      <c r="R33">
+        <v>1</v>
+      </c>
+      <c r="S33" t="s">
+        <v>20</v>
+      </c>
+      <c r="X33">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46052</v>
       </c>
@@ -2461,46 +2564,49 @@
         <v>3</v>
       </c>
       <c r="H34">
+        <v>3</v>
+      </c>
+      <c r="I34">
         <v>35</v>
       </c>
-      <c r="I34">
-        <v>3</v>
-      </c>
       <c r="J34">
+        <v>3</v>
+      </c>
+      <c r="K34">
         <v>26</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>30</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>10</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>21</v>
       </c>
-      <c r="N34">
-        <v>3</v>
-      </c>
       <c r="O34">
+        <v>3</v>
+      </c>
+      <c r="P34">
         <v>26</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>32</v>
       </c>
-      <c r="Q34">
-        <v>1</v>
-      </c>
-      <c r="R34" t="s">
-        <v>20</v>
+      <c r="R34">
+        <v>1</v>
       </c>
       <c r="S34" t="s">
         <v>20</v>
       </c>
-      <c r="W34">
+      <c r="T34" t="s">
+        <v>20</v>
+      </c>
+      <c r="X34">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46053</v>
       </c>
@@ -2523,34 +2629,37 @@
         <v>4</v>
       </c>
       <c r="H35">
+        <v>4</v>
+      </c>
+      <c r="I35">
         <v>32</v>
       </c>
-      <c r="I35">
-        <v>3</v>
-      </c>
       <c r="J35">
+        <v>3</v>
+      </c>
+      <c r="K35">
         <v>34</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>29</v>
       </c>
-      <c r="N35">
-        <v>3</v>
-      </c>
       <c r="O35">
+        <v>3</v>
+      </c>
+      <c r="P35">
         <v>28</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>35</v>
       </c>
-      <c r="Q35">
-        <v>1</v>
-      </c>
-      <c r="W35">
+      <c r="R35">
+        <v>1</v>
+      </c>
+      <c r="X35">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>46054</v>
       </c>
@@ -2573,40 +2682,43 @@
         <v>5</v>
       </c>
       <c r="H36">
+        <v>5</v>
+      </c>
+      <c r="I36">
         <v>30</v>
       </c>
-      <c r="I36">
-        <v>3</v>
-      </c>
       <c r="J36">
+        <v>3</v>
+      </c>
+      <c r="K36">
         <v>29</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>24</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>10.75</v>
       </c>
-      <c r="M36">
+      <c r="N36">
         <v>21</v>
       </c>
-      <c r="N36">
-        <v>2</v>
-      </c>
       <c r="O36">
+        <v>2</v>
+      </c>
+      <c r="P36">
         <v>22</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>33</v>
       </c>
-      <c r="Q36">
-        <v>1</v>
-      </c>
-      <c r="W36">
+      <c r="R36">
+        <v>1</v>
+      </c>
+      <c r="X36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>46064</v>
       </c>
@@ -2629,40 +2741,43 @@
         <v>1</v>
       </c>
       <c r="H37">
+        <v>6</v>
+      </c>
+      <c r="I37">
         <v>25</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>4</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>42</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>33</v>
       </c>
-      <c r="M37">
+      <c r="N37">
         <v>21</v>
       </c>
-      <c r="N37">
-        <v>3</v>
-      </c>
       <c r="O37">
+        <v>3</v>
+      </c>
+      <c r="P37">
         <v>29</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
         <v>33</v>
       </c>
-      <c r="Q37">
-        <v>1</v>
-      </c>
-      <c r="R37" t="s">
-        <v>20</v>
-      </c>
-      <c r="W37">
+      <c r="R37">
+        <v>1</v>
+      </c>
+      <c r="S37" t="s">
+        <v>20</v>
+      </c>
+      <c r="X37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>46065</v>
       </c>
@@ -2685,43 +2800,46 @@
         <v>2</v>
       </c>
       <c r="H38">
+        <v>7</v>
+      </c>
+      <c r="I38">
         <v>25</v>
       </c>
-      <c r="I38">
-        <v>3</v>
-      </c>
       <c r="J38">
+        <v>3</v>
+      </c>
+      <c r="K38">
         <v>33</v>
       </c>
-      <c r="K38">
+      <c r="L38">
         <v>24</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>9.75</v>
       </c>
-      <c r="M38">
+      <c r="N38">
         <v>21</v>
       </c>
-      <c r="N38">
-        <v>2</v>
-      </c>
       <c r="O38">
+        <v>2</v>
+      </c>
+      <c r="P38">
         <v>24</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
         <v>29</v>
       </c>
-      <c r="Q38">
-        <v>1</v>
-      </c>
-      <c r="R38" t="s">
-        <v>20</v>
-      </c>
-      <c r="W38">
+      <c r="R38">
+        <v>1</v>
+      </c>
+      <c r="S38" t="s">
+        <v>20</v>
+      </c>
+      <c r="X38">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>46066</v>
       </c>
@@ -2744,34 +2862,37 @@
         <v>3</v>
       </c>
       <c r="H39">
+        <v>8</v>
+      </c>
+      <c r="I39">
         <v>25</v>
       </c>
-      <c r="I39">
-        <v>2</v>
-      </c>
       <c r="J39">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="K39">
         <v>22</v>
       </c>
-      <c r="N39">
-        <v>3</v>
+      <c r="L39">
+        <v>22</v>
       </c>
       <c r="O39">
+        <v>3</v>
+      </c>
+      <c r="P39">
         <v>25</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
         <v>28</v>
       </c>
-      <c r="Q39">
-        <v>1</v>
-      </c>
-      <c r="W39">
+      <c r="R39">
+        <v>1</v>
+      </c>
+      <c r="X39">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>46067</v>
       </c>
@@ -2794,40 +2915,43 @@
         <v>4</v>
       </c>
       <c r="H40">
+        <v>9</v>
+      </c>
+      <c r="I40">
         <v>21</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>4</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>36</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>32</v>
       </c>
-      <c r="M40">
+      <c r="N40">
         <v>21</v>
       </c>
-      <c r="N40">
-        <v>2</v>
-      </c>
       <c r="O40">
+        <v>2</v>
+      </c>
+      <c r="P40">
         <v>22</v>
       </c>
-      <c r="P40">
+      <c r="Q40">
         <v>28</v>
       </c>
-      <c r="Q40">
-        <v>1</v>
-      </c>
-      <c r="R40" t="s">
-        <v>20</v>
-      </c>
-      <c r="W40">
+      <c r="R40">
+        <v>1</v>
+      </c>
+      <c r="S40" t="s">
+        <v>20</v>
+      </c>
+      <c r="X40">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>46068</v>
       </c>
@@ -2850,59 +2974,62 @@
         <v>5</v>
       </c>
       <c r="H41">
+        <v>10</v>
+      </c>
+      <c r="I41">
         <v>22</v>
       </c>
-      <c r="I41">
-        <v>3</v>
-      </c>
       <c r="J41">
+        <v>3</v>
+      </c>
+      <c r="K41">
         <v>34</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <v>33</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>10.7</v>
       </c>
-      <c r="M41">
+      <c r="N41">
         <v>21</v>
       </c>
-      <c r="N41">
-        <v>3</v>
-      </c>
       <c r="O41">
+        <v>3</v>
+      </c>
+      <c r="P41">
         <v>26</v>
       </c>
-      <c r="P41">
+      <c r="Q41">
         <v>28</v>
       </c>
-      <c r="Q41">
-        <v>1</v>
-      </c>
-      <c r="S41" t="s">
-        <v>20</v>
-      </c>
-      <c r="W41">
+      <c r="R41">
+        <v>1</v>
+      </c>
+      <c r="T41" t="s">
+        <v>20</v>
+      </c>
+      <c r="X41">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
     </row>
